--- a/PROJECT MAOLIN/import_product 1.xlsx
+++ b/PROJECT MAOLIN/import_product 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\web\craveva-staging\PROJECT MAOLIN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8730202-0630-4F17-BABF-AD8F0EB4225A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982FA5C9-EB6A-4EE7-85E0-810E437D62CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7824,7 +7824,7 @@
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="105.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
